--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92541708305</v>
+        <v>46157.93117167481</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117167481</v>
+        <v>46157.93369572294</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93369572294</v>
+        <v>46157.93673981469</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93673981469</v>
+        <v>46158.28195577213</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28195577213</v>
+        <v>46158.2971985622</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2971985622</v>
+        <v>46158.29792263737</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29792263737</v>
+        <v>46158.3335699946</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3335699946</v>
+        <v>46158.37211537073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/24. ДИО кап.рем/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211537073</v>
+        <v>46158.37268479096</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
